--- a/tests/regression_artifacts/downloads/email_03152025140315/current/HAW639600873.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025140315/current/HAW639600873.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -786,11 +786,11 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>BLOCKICE Highlight Ombre Lace Front Wig Human Hair Wigs for Black (1 items)</t>
+          <t>BLOCKICE Highlight Ombre Lace Front Wig Human Hair Wigs for Black (+1 more) (2 items)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="inlineStr"/>
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>41.99</v>
+        <v>216.69</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>41.99</v>
+        <v>433.38</v>
       </c>
       <c r="Q2" s="3">
         <f>O2*K2</f>
@@ -814,7 +814,7 @@
         <v/>
       </c>
       <c r="S2" s="3" t="n">
-        <v>81.15000000000001</v>
+        <v>454.38</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>21</v>
@@ -933,150 +933,120 @@
       <c r="AK3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>113-0728579-9633009</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>SYNTHETIC HAIR</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>67041900</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67041900</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Faux Locs Crochet Hair Soft Locs 30 inch 6 Packs Long Pre Looped Crochet (1 items)</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>67041100</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>AMZ-4</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Queen Story 26 Inch Lace Front Wigs Human Hair 13 x 4 Straight Human</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="Q4" s="3">
+      <c r="O4" s="5" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="Q4" s="5">
         <f>O4*K4</f>
         <v/>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="5">
         <f>P4-Q4</f>
         <v/>
       </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="2" t="n"/>
-      <c r="Y4" s="2" t="n"/>
-      <c r="Z4" s="2" t="n"/>
-      <c r="AA4" s="2" t="n"/>
-      <c r="AB4" s="2" t="n"/>
-      <c r="AC4" s="2" t="n"/>
-      <c r="AD4" s="2" t="n"/>
-      <c r="AE4" s="2" t="n"/>
-      <c r="AF4" s="2" t="n"/>
-      <c r="AG4" s="2" t="n"/>
-      <c r="AH4" s="2" t="n"/>
-      <c r="AI4" s="2" t="n"/>
-      <c r="AJ4" s="2" t="n"/>
-      <c r="AK4" s="2" t="inlineStr">
-        <is>
-          <t>67041900</t>
-        </is>
-      </c>
+      <c r="S4" s="4" t="n"/>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="4" t="n"/>
+      <c r="X4" s="4" t="n"/>
+      <c r="Y4" s="4" t="n"/>
+      <c r="Z4" s="4" t="n"/>
+      <c r="AA4" s="4" t="n"/>
+      <c r="AB4" s="4" t="n"/>
+      <c r="AC4" s="4" t="n"/>
+      <c r="AD4" s="4" t="n"/>
+      <c r="AE4" s="4" t="n"/>
+      <c r="AF4" s="4" t="n"/>
+      <c r="AG4" s="4" t="n"/>
+      <c r="AH4" s="4" t="n"/>
+      <c r="AI4" s="4" t="n"/>
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>67041900</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>AMZ-3</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Faux Locs Crochet Hair Soft Locs 30 inch 6 Packs Long Pre Looped Crochet</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="Q5" s="5">
-        <f>O5*K5</f>
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>SUBTOTAL (GROUPED)</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="7">
+        <f>P2</f>
         <v/>
       </c>
-      <c r="R5" s="5">
-        <f>P5-Q5</f>
+      <c r="Q5" s="7">
+        <f>Q2</f>
         <v/>
       </c>
-      <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n"/>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n"/>
-      <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n"/>
-      <c r="AF5" s="4" t="n"/>
-      <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="4" t="n"/>
-      <c r="AI5" s="4" t="n"/>
-      <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="4" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
+      <c r="AA5" s="6" t="n"/>
+      <c r="AB5" s="6" t="n"/>
+      <c r="AC5" s="6" t="n"/>
+      <c r="AD5" s="6" t="n"/>
+      <c r="AE5" s="6" t="n"/>
+      <c r="AF5" s="6" t="n"/>
+      <c r="AG5" s="6" t="n"/>
+      <c r="AH5" s="6" t="n"/>
+      <c r="AI5" s="6" t="n"/>
+      <c r="AJ5" s="6" t="n"/>
+      <c r="AK5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -1090,7 +1060,7 @@
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>SUBTOTAL (GROUPED)</t>
+          <t>SUBTOTAL (DETAILS)</t>
         </is>
       </c>
       <c r="K6" s="6" t="n"/>
@@ -1099,11 +1069,11 @@
       <c r="N6" s="6" t="n"/>
       <c r="O6" s="6" t="n"/>
       <c r="P6" s="7">
-        <f>P2+P4</f>
+        <f>SUM(P2:P4)-P5</f>
         <v/>
       </c>
       <c r="Q6" s="7">
-        <f>Q2+Q4</f>
+        <f>SUM(Q2:Q4)-Q5</f>
         <v/>
       </c>
       <c r="R6" s="6" t="n"/>
@@ -1128,104 +1098,100 @@
       <c r="AK6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>SUBTOTAL (DETAILS)</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="7">
-        <f>SUM(P2:P5)-P6</f>
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>GROUP VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="9">
+        <f>P5-P6</f>
         <v/>
       </c>
-      <c r="Q7" s="7">
-        <f>SUM(Q2:Q5)-Q6</f>
+      <c r="Q7" s="9">
+        <f>Q5-Q6</f>
         <v/>
       </c>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>GROUP VERIFICATION</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="9">
-        <f>P6-P7</f>
-        <v/>
-      </c>
-      <c r="Q8" s="9">
-        <f>Q6-Q7</f>
-        <v/>
-      </c>
-      <c r="R8" s="8" t="n"/>
-      <c r="S8" s="8" t="n"/>
-      <c r="T8" s="8" t="n"/>
-      <c r="U8" s="8" t="n"/>
-      <c r="V8" s="8" t="n"/>
-      <c r="W8" s="8" t="n"/>
-      <c r="X8" s="8" t="n"/>
-      <c r="Y8" s="8" t="n"/>
-      <c r="Z8" s="8" t="n"/>
-      <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="8" t="n"/>
-      <c r="AC8" s="8" t="n"/>
-      <c r="AD8" s="8" t="n"/>
-      <c r="AE8" s="8" t="n"/>
-      <c r="AF8" s="8" t="n"/>
-      <c r="AG8" s="8" t="n"/>
-      <c r="AH8" s="8" t="n"/>
-      <c r="AI8" s="8" t="n"/>
-      <c r="AJ8" s="8" t="n"/>
-      <c r="AK8" s="8" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8" t="n"/>
+      <c r="AI7" s="8" t="n"/>
+      <c r="AJ7" s="8" t="n"/>
+      <c r="AK7" s="8" t="n"/>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INTERNAL FREIGHT</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
+      <c r="T9" s="6" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="6" t="n"/>
+      <c r="Z9" s="6" t="n"/>
+      <c r="AA9" s="6" t="n"/>
+      <c r="AB9" s="6" t="n"/>
+      <c r="AC9" s="6" t="n"/>
+      <c r="AD9" s="6" t="n"/>
+      <c r="AE9" s="6" t="n"/>
+      <c r="AF9" s="6" t="n"/>
+      <c r="AG9" s="6" t="n"/>
+      <c r="AH9" s="6" t="n"/>
+      <c r="AI9" s="6" t="n"/>
+      <c r="AJ9" s="6" t="n"/>
+      <c r="AK9" s="6" t="n"/>
+    </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
@@ -1238,7 +1204,7 @@
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>TOTAL INTERNAL FREIGHT</t>
+          <t>TOTAL INSURANCE</t>
         </is>
       </c>
       <c r="K10" s="6" t="n"/>
@@ -1247,7 +1213,7 @@
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="6" t="n"/>
       <c r="P10" s="7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="7" t="n"/>
       <c r="R10" s="6" t="n"/>
@@ -1283,7 +1249,7 @@
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>TOTAL INSURANCE</t>
+          <t>TOTAL OTHER COST</t>
         </is>
       </c>
       <c r="K11" s="6" t="n"/>
@@ -1328,7 +1294,7 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>TOTAL OTHER COST</t>
+          <t>TOTAL DEDUCTION</t>
         </is>
       </c>
       <c r="K12" s="6" t="n"/>
@@ -1373,7 +1339,7 @@
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>TOTAL DEDUCTION</t>
+          <t>ADJUSTMENTS</t>
         </is>
       </c>
       <c r="K13" s="6" t="n"/>
@@ -1381,10 +1347,14 @@
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
       <c r="O13" s="6" t="n"/>
-      <c r="P13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7" t="n"/>
+      <c r="P13" s="7">
+        <f>(T2+U2+V2-W2)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="7">
+        <f>(T2+U2+V2-W2)</f>
+        <v/>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
@@ -1406,56 +1376,56 @@
       <c r="AJ13" s="6" t="n"/>
       <c r="AK13" s="6" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="7">
-        <f>(T2+U2+V2-W2)</f>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>NET TOTAL</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="7">
+        <f>P5+P13</f>
         <v/>
       </c>
-      <c r="Q14" s="7">
-        <f>(T2+U2+V2-W2)</f>
+      <c r="Q15" s="7">
+        <f>Q5+Q13</f>
         <v/>
       </c>
-      <c r="R14" s="6" t="n"/>
-      <c r="S14" s="6" t="n"/>
-      <c r="T14" s="6" t="n"/>
-      <c r="U14" s="6" t="n"/>
-      <c r="V14" s="6" t="n"/>
-      <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
-      <c r="AA14" s="6" t="n"/>
-      <c r="AB14" s="6" t="n"/>
-      <c r="AC14" s="6" t="n"/>
-      <c r="AD14" s="6" t="n"/>
-      <c r="AE14" s="6" t="n"/>
-      <c r="AF14" s="6" t="n"/>
-      <c r="AG14" s="6" t="n"/>
-      <c r="AH14" s="6" t="n"/>
-      <c r="AI14" s="6" t="n"/>
-      <c r="AJ14" s="6" t="n"/>
-      <c r="AK14" s="6" t="n"/>
-    </row>
-    <row r="15"/>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="6" t="n"/>
+      <c r="AB15" s="6" t="n"/>
+      <c r="AC15" s="6" t="n"/>
+      <c r="AD15" s="6" t="n"/>
+      <c r="AE15" s="6" t="n"/>
+      <c r="AF15" s="6" t="n"/>
+      <c r="AG15" s="6" t="n"/>
+      <c r="AH15" s="6" t="n"/>
+      <c r="AI15" s="6" t="n"/>
+      <c r="AJ15" s="6" t="n"/>
+      <c r="AK15" s="6" t="n"/>
+    </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
@@ -1468,7 +1438,7 @@
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>NET TOTAL</t>
+          <t>INVOICE TOTAL</t>
         </is>
       </c>
       <c r="K16" s="6" t="n"/>
@@ -1477,13 +1447,10 @@
       <c r="N16" s="6" t="n"/>
       <c r="O16" s="6" t="n"/>
       <c r="P16" s="7">
-        <f>P6+P14</f>
+        <f>S2</f>
         <v/>
       </c>
-      <c r="Q16" s="7">
-        <f>Q6+Q14</f>
-        <v/>
-      </c>
+      <c r="Q16" s="7" t="n"/>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
@@ -1505,189 +1472,188 @@
       <c r="AJ16" s="6" t="n"/>
       <c r="AK16" s="6" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>INVOICE TOTAL</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="7">
-        <f>S2</f>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>VARIANCE CHECK</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="11">
+        <f>S2-P15</f>
         <v/>
       </c>
-      <c r="Q17" s="7" t="n"/>
-      <c r="R17" s="6" t="n"/>
-      <c r="S17" s="6" t="n"/>
-      <c r="T17" s="6" t="n"/>
-      <c r="U17" s="6" t="n"/>
-      <c r="V17" s="6" t="n"/>
-      <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
-      <c r="AA17" s="6" t="n"/>
-      <c r="AB17" s="6" t="n"/>
-      <c r="AC17" s="6" t="n"/>
-      <c r="AD17" s="6" t="n"/>
-      <c r="AE17" s="6" t="n"/>
-      <c r="AF17" s="6" t="n"/>
-      <c r="AG17" s="6" t="n"/>
-      <c r="AH17" s="6" t="n"/>
-      <c r="AI17" s="6" t="n"/>
-      <c r="AJ17" s="6" t="n"/>
-      <c r="AK17" s="6" t="n"/>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>VARIANCE CHECK</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="11">
-        <f>S2-P16</f>
+      <c r="Q18" s="11">
+        <f>S2-Q15</f>
         <v/>
       </c>
-      <c r="Q19" s="11">
-        <f>S2-Q16</f>
-        <v/>
-      </c>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="10" t="n"/>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="10" t="n"/>
-      <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="10" t="n"/>
-      <c r="AA19" s="10" t="n"/>
-      <c r="AB19" s="10" t="n"/>
-      <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="10" t="n"/>
-      <c r="AE19" s="10" t="n"/>
-      <c r="AF19" s="10" t="n"/>
-      <c r="AG19" s="10" t="n"/>
-      <c r="AH19" s="10" t="n"/>
-      <c r="AI19" s="10" t="n"/>
-      <c r="AJ19" s="10" t="n"/>
-      <c r="AK19" s="10" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="10" t="n"/>
+      <c r="AG18" s="10" t="n"/>
+      <c r="AH18" s="10" t="n"/>
+      <c r="AI18" s="10" t="n"/>
+      <c r="AJ18" s="10" t="n"/>
+      <c r="AK18" s="10" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>INVOICE NOTES: Structural item count mismatch: 5 price lines found between section markers but 4 items extracted</t>
         </is>
       </c>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="12" t="n"/>
-      <c r="R21" s="12" t="n"/>
-      <c r="S21" s="12" t="n"/>
-      <c r="T21" s="12" t="n"/>
-      <c r="U21" s="12" t="n"/>
-      <c r="V21" s="12" t="n"/>
-      <c r="W21" s="12" t="n"/>
-      <c r="X21" s="12" t="n"/>
-      <c r="Y21" s="12" t="n"/>
-      <c r="Z21" s="12" t="n"/>
-      <c r="AA21" s="12" t="n"/>
-      <c r="AB21" s="12" t="n"/>
-      <c r="AC21" s="12" t="n"/>
-      <c r="AD21" s="12" t="n"/>
-      <c r="AE21" s="12" t="n"/>
-      <c r="AF21" s="12" t="n"/>
-      <c r="AG21" s="12" t="n"/>
-      <c r="AH21" s="12" t="n"/>
-      <c r="AI21" s="12" t="n"/>
-      <c r="AJ21" s="12" t="n"/>
-      <c r="AK21" s="12" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="n"/>
+      <c r="P20" s="12" t="n"/>
+      <c r="Q20" s="12" t="n"/>
+      <c r="R20" s="12" t="n"/>
+      <c r="S20" s="12" t="n"/>
+      <c r="T20" s="12" t="n"/>
+      <c r="U20" s="12" t="n"/>
+      <c r="V20" s="12" t="n"/>
+      <c r="W20" s="12" t="n"/>
+      <c r="X20" s="12" t="n"/>
+      <c r="Y20" s="12" t="n"/>
+      <c r="Z20" s="12" t="n"/>
+      <c r="AA20" s="12" t="n"/>
+      <c r="AB20" s="12" t="n"/>
+      <c r="AC20" s="12" t="n"/>
+      <c r="AD20" s="12" t="n"/>
+      <c r="AE20" s="12" t="n"/>
+      <c r="AF20" s="12" t="n"/>
+      <c r="AG20" s="12" t="n"/>
+      <c r="AH20" s="12" t="n"/>
+      <c r="AI20" s="12" t="n"/>
+      <c r="AJ20" s="12" t="n"/>
+      <c r="AK20" s="12" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>DUTY ESTIMATION (Classification Cross-Check)</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
+      <c r="O22" s="14" t="n"/>
+      <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+      <c r="R22" s="14" t="n"/>
+      <c r="S22" s="14" t="n"/>
+      <c r="T22" s="14" t="n"/>
+      <c r="U22" s="14" t="n"/>
+      <c r="V22" s="14" t="n"/>
+      <c r="W22" s="14" t="n"/>
+      <c r="X22" s="14" t="n"/>
+      <c r="Y22" s="14" t="n"/>
+      <c r="Z22" s="14" t="n"/>
+      <c r="AA22" s="14" t="n"/>
+      <c r="AB22" s="14" t="n"/>
+      <c r="AC22" s="14" t="n"/>
+      <c r="AD22" s="14" t="n"/>
+      <c r="AE22" s="14" t="n"/>
+      <c r="AF22" s="14" t="n"/>
+      <c r="AG22" s="14" t="n"/>
+      <c r="AH22" s="14" t="n"/>
+      <c r="AI22" s="14" t="n"/>
+      <c r="AJ22" s="14" t="n"/>
+      <c r="AK22" s="14" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="14" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-      <c r="H23" s="14" t="n"/>
-      <c r="I23" s="14" t="n"/>
-      <c r="J23" s="14" t="inlineStr">
-        <is>
-          <t>DUTY ESTIMATION (Classification Cross-Check)</t>
-        </is>
-      </c>
-      <c r="K23" s="14" t="n"/>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="14" t="n"/>
-      <c r="N23" s="14" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
-      <c r="Q23" s="14" t="n"/>
-      <c r="R23" s="14" t="n"/>
-      <c r="S23" s="14" t="n"/>
-      <c r="T23" s="14" t="n"/>
-      <c r="U23" s="14" t="n"/>
-      <c r="V23" s="14" t="n"/>
-      <c r="W23" s="14" t="n"/>
-      <c r="X23" s="14" t="n"/>
-      <c r="Y23" s="14" t="n"/>
-      <c r="Z23" s="14" t="n"/>
-      <c r="AA23" s="14" t="n"/>
-      <c r="AB23" s="14" t="n"/>
-      <c r="AC23" s="14" t="n"/>
-      <c r="AD23" s="14" t="n"/>
-      <c r="AE23" s="14" t="n"/>
-      <c r="AF23" s="14" t="n"/>
-      <c r="AG23" s="14" t="n"/>
-      <c r="AH23" s="14" t="n"/>
-      <c r="AI23" s="14" t="n"/>
-      <c r="AJ23" s="14" t="n"/>
-      <c r="AK23" s="14" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>CIF (USD) = InvTotal + Freight + Insurance</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="17" t="n">
+        <v>475.38</v>
+      </c>
+      <c r="Q23" s="15" t="n"/>
+      <c r="R23" s="15" t="n"/>
+      <c r="S23" s="15" t="n"/>
+      <c r="T23" s="15" t="n"/>
+      <c r="U23" s="15" t="n"/>
+      <c r="V23" s="15" t="n"/>
+      <c r="W23" s="15" t="n"/>
+      <c r="X23" s="15" t="n"/>
+      <c r="Y23" s="15" t="n"/>
+      <c r="Z23" s="15" t="n"/>
+      <c r="AA23" s="15" t="n"/>
+      <c r="AB23" s="15" t="n"/>
+      <c r="AC23" s="15" t="n"/>
+      <c r="AD23" s="15" t="n"/>
+      <c r="AE23" s="15" t="n"/>
+      <c r="AF23" s="15" t="n"/>
+      <c r="AG23" s="15" t="n"/>
+      <c r="AH23" s="15" t="n"/>
+      <c r="AI23" s="15" t="n"/>
+      <c r="AJ23" s="15" t="n"/>
+      <c r="AK23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="n"/>
@@ -1701,7 +1667,7 @@
       <c r="I24" s="15" t="n"/>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>CIF (USD) = InvTotal + Freight + Insurance</t>
+          <t>CIF (XCD) = CIF × 2.7169</t>
         </is>
       </c>
       <c r="K24" s="15" t="n"/>
@@ -1710,7 +1676,7 @@
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="17" t="n">
-        <v>102.15</v>
+        <v>1291.56</v>
       </c>
       <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
@@ -1746,7 +1712,7 @@
       <c r="I25" s="15" t="n"/>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>CIF (XCD) = CIF × 2.7169</t>
+          <t>CET (20%) — Tariff 67041100</t>
         </is>
       </c>
       <c r="K25" s="15" t="n"/>
@@ -1755,7 +1721,7 @@
       <c r="N25" s="15" t="n"/>
       <c r="O25" s="15" t="n"/>
       <c r="P25" s="17" t="n">
-        <v>277.53</v>
+        <v>258.31</v>
       </c>
       <c r="Q25" s="15" t="n"/>
       <c r="R25" s="15" t="n"/>
@@ -1791,7 +1757,7 @@
       <c r="I26" s="15" t="n"/>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>CET (weighted avg 20.0%)</t>
+          <t>CSC (6%)</t>
         </is>
       </c>
       <c r="K26" s="15" t="n"/>
@@ -1800,7 +1766,7 @@
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="17" t="n">
-        <v>55.51</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="Q26" s="15" t="n"/>
       <c r="R26" s="15" t="n"/>
@@ -1836,7 +1802,7 @@
       <c r="I27" s="15" t="n"/>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 67041100: 20% CET (70% of value)</t>
+          <t>VAT (15%) on CIF+CET+CSC</t>
         </is>
       </c>
       <c r="K27" s="15" t="n"/>
@@ -1845,7 +1811,7 @@
       <c r="N27" s="15" t="n"/>
       <c r="O27" s="15" t="n"/>
       <c r="P27" s="17" t="n">
-        <v>38.75</v>
+        <v>244.1</v>
       </c>
       <c r="Q27" s="15" t="n"/>
       <c r="R27" s="15" t="n"/>
@@ -1870,49 +1836,49 @@
       <c r="AK27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └ 67041900: 20% CET (30% of value)</t>
-        </is>
-      </c>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="17" t="n">
-        <v>16.76</v>
-      </c>
-      <c r="Q28" s="15" t="n"/>
-      <c r="R28" s="15" t="n"/>
-      <c r="S28" s="15" t="n"/>
-      <c r="T28" s="15" t="n"/>
-      <c r="U28" s="15" t="n"/>
-      <c r="V28" s="15" t="n"/>
-      <c r="W28" s="15" t="n"/>
-      <c r="X28" s="15" t="n"/>
-      <c r="Y28" s="15" t="n"/>
-      <c r="Z28" s="15" t="n"/>
-      <c r="AA28" s="15" t="n"/>
-      <c r="AB28" s="15" t="n"/>
-      <c r="AC28" s="15" t="n"/>
-      <c r="AD28" s="15" t="n"/>
-      <c r="AE28" s="15" t="n"/>
-      <c r="AF28" s="15" t="n"/>
-      <c r="AG28" s="15" t="n"/>
-      <c r="AH28" s="15" t="n"/>
-      <c r="AI28" s="15" t="n"/>
-      <c r="AJ28" s="15" t="n"/>
-      <c r="AK28" s="15" t="n"/>
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>ESTIMATED TOTAL DUTIES</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
+      <c r="P28" s="19" t="n">
+        <v>579.9</v>
+      </c>
+      <c r="Q28" s="18" t="n"/>
+      <c r="R28" s="18" t="n"/>
+      <c r="S28" s="18" t="n"/>
+      <c r="T28" s="18" t="n"/>
+      <c r="U28" s="18" t="n"/>
+      <c r="V28" s="18" t="n"/>
+      <c r="W28" s="18" t="n"/>
+      <c r="X28" s="18" t="n"/>
+      <c r="Y28" s="18" t="n"/>
+      <c r="Z28" s="18" t="n"/>
+      <c r="AA28" s="18" t="n"/>
+      <c r="AB28" s="18" t="n"/>
+      <c r="AC28" s="18" t="n"/>
+      <c r="AD28" s="18" t="n"/>
+      <c r="AE28" s="18" t="n"/>
+      <c r="AF28" s="18" t="n"/>
+      <c r="AG28" s="18" t="n"/>
+      <c r="AH28" s="18" t="n"/>
+      <c r="AI28" s="18" t="n"/>
+      <c r="AJ28" s="18" t="n"/>
+      <c r="AK28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n"/>
@@ -1926,7 +1892,7 @@
       <c r="I29" s="15" t="n"/>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>CSC (6%)</t>
+          <t>Effective Duty Rate</t>
         </is>
       </c>
       <c r="K29" s="15" t="n"/>
@@ -1934,8 +1900,8 @@
       <c r="M29" s="15" t="n"/>
       <c r="N29" s="15" t="n"/>
       <c r="O29" s="15" t="n"/>
-      <c r="P29" s="17" t="n">
-        <v>16.65</v>
+      <c r="P29" s="20" t="n">
+        <v>0.448991916751835</v>
       </c>
       <c r="Q29" s="15" t="n"/>
       <c r="R29" s="15" t="n"/>
@@ -1959,170 +1925,214 @@
       <c r="AJ29" s="15" t="n"/>
       <c r="AK29" s="15" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>VAT (15%) on CIF+CET+CSC</t>
-        </is>
-      </c>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="17" t="n">
-        <v>52.45</v>
-      </c>
-      <c r="Q30" s="15" t="n"/>
-      <c r="R30" s="15" t="n"/>
-      <c r="S30" s="15" t="n"/>
-      <c r="T30" s="15" t="n"/>
-      <c r="U30" s="15" t="n"/>
-      <c r="V30" s="15" t="n"/>
-      <c r="W30" s="15" t="n"/>
-      <c r="X30" s="15" t="n"/>
-      <c r="Y30" s="15" t="n"/>
-      <c r="Z30" s="15" t="n"/>
-      <c r="AA30" s="15" t="n"/>
-      <c r="AB30" s="15" t="n"/>
-      <c r="AC30" s="15" t="n"/>
-      <c r="AD30" s="15" t="n"/>
-      <c r="AE30" s="15" t="n"/>
-      <c r="AF30" s="15" t="n"/>
-      <c r="AG30" s="15" t="n"/>
-      <c r="AH30" s="15" t="n"/>
-      <c r="AI30" s="15" t="n"/>
-      <c r="AJ30" s="15" t="n"/>
-      <c r="AK30" s="15" t="n"/>
-    </row>
+    <row r="30"/>
     <row r="31">
-      <c r="A31" s="18" t="n"/>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="14" t="inlineStr">
-        <is>
-          <t>ESTIMATED TOTAL DUTIES</t>
-        </is>
-      </c>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="18" t="n"/>
-      <c r="P31" s="19" t="n">
-        <v>124.61</v>
-      </c>
-      <c r="Q31" s="18" t="n"/>
-      <c r="R31" s="18" t="n"/>
-      <c r="S31" s="18" t="n"/>
-      <c r="T31" s="18" t="n"/>
-      <c r="U31" s="18" t="n"/>
-      <c r="V31" s="18" t="n"/>
-      <c r="W31" s="18" t="n"/>
-      <c r="X31" s="18" t="n"/>
-      <c r="Y31" s="18" t="n"/>
-      <c r="Z31" s="18" t="n"/>
-      <c r="AA31" s="18" t="n"/>
-      <c r="AB31" s="18" t="n"/>
-      <c r="AC31" s="18" t="n"/>
-      <c r="AD31" s="18" t="n"/>
-      <c r="AE31" s="18" t="n"/>
-      <c r="AF31" s="18" t="n"/>
-      <c r="AG31" s="18" t="n"/>
-      <c r="AH31" s="18" t="n"/>
-      <c r="AI31" s="18" t="n"/>
-      <c r="AJ31" s="18" t="n"/>
-      <c r="AK31" s="18" t="n"/>
+      <c r="A31" s="21" t="n"/>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="21" t="n"/>
+      <c r="F31" s="21" t="n"/>
+      <c r="G31" s="21" t="n"/>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="21" t="n"/>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>Items on other declaration(s) (2 items)</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="n"/>
+      <c r="L31" s="21" t="n"/>
+      <c r="M31" s="21" t="n"/>
+      <c r="N31" s="21" t="n"/>
+      <c r="O31" s="21" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="21" t="n"/>
+      <c r="R31" s="21" t="n"/>
+      <c r="S31" s="21" t="n"/>
+      <c r="T31" s="21" t="n"/>
+      <c r="U31" s="21" t="n"/>
+      <c r="V31" s="21" t="n"/>
+      <c r="W31" s="21" t="n"/>
+      <c r="X31" s="21" t="n"/>
+      <c r="Y31" s="21" t="n"/>
+      <c r="Z31" s="21" t="n"/>
+      <c r="AA31" s="21" t="n"/>
+      <c r="AB31" s="21" t="n"/>
+      <c r="AC31" s="21" t="n"/>
+      <c r="AD31" s="21" t="n"/>
+      <c r="AE31" s="21" t="n"/>
+      <c r="AF31" s="21" t="n"/>
+      <c r="AG31" s="21" t="n"/>
+      <c r="AH31" s="21" t="n"/>
+      <c r="AI31" s="21" t="n"/>
+      <c r="AJ31" s="21" t="n"/>
+      <c r="AK31" s="21" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>Effective Duty Rate</t>
-        </is>
-      </c>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="20" t="n">
-        <v>0.4489965048823551</v>
-      </c>
-      <c r="Q32" s="15" t="n"/>
-      <c r="R32" s="15" t="n"/>
-      <c r="S32" s="15" t="n"/>
-      <c r="T32" s="15" t="n"/>
-      <c r="U32" s="15" t="n"/>
-      <c r="V32" s="15" t="n"/>
-      <c r="W32" s="15" t="n"/>
-      <c r="X32" s="15" t="n"/>
-      <c r="Y32" s="15" t="n"/>
-      <c r="Z32" s="15" t="n"/>
-      <c r="AA32" s="15" t="n"/>
-      <c r="AB32" s="15" t="n"/>
-      <c r="AC32" s="15" t="n"/>
-      <c r="AD32" s="15" t="n"/>
-      <c r="AE32" s="15" t="n"/>
-      <c r="AF32" s="15" t="n"/>
-      <c r="AG32" s="15" t="n"/>
-      <c r="AH32" s="15" t="n"/>
-      <c r="AI32" s="15" t="n"/>
-      <c r="AJ32" s="15" t="n"/>
-      <c r="AK32" s="15" t="n"/>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="21" t="n"/>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>WIGS</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>67041100</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="21" t="n"/>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>Aauerep Deep Wave Lace Front Wigs Human Hair Wigs for Women (1 items)</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="21" t="n"/>
+      <c r="M32" s="21" t="n"/>
+      <c r="N32" s="21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O32" s="22" t="n">
+        <v>104.97</v>
+      </c>
+      <c r="P32" s="22" t="n">
+        <v>104.97</v>
+      </c>
+      <c r="Q32" s="22" t="n"/>
+      <c r="R32" s="22" t="n"/>
+      <c r="S32" s="22" t="n"/>
+      <c r="T32" s="22" t="n"/>
+      <c r="U32" s="22" t="n"/>
+      <c r="V32" s="22" t="n"/>
+      <c r="W32" s="22" t="n"/>
+      <c r="X32" s="21" t="n"/>
+      <c r="Y32" s="21" t="n"/>
+      <c r="Z32" s="21" t="n"/>
+      <c r="AA32" s="21" t="n"/>
+      <c r="AB32" s="21" t="n"/>
+      <c r="AC32" s="21" t="n"/>
+      <c r="AD32" s="21" t="n"/>
+      <c r="AE32" s="21" t="n"/>
+      <c r="AF32" s="21" t="n"/>
+      <c r="AG32" s="21" t="n"/>
+      <c r="AH32" s="21" t="n"/>
+      <c r="AI32" s="21" t="n"/>
+      <c r="AJ32" s="21" t="n"/>
+      <c r="AK32" s="21" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="23" t="n"/>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>AMZ-2</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>Aauerep Deep Wave Lace Front Wigs Human Hair Wigs for Women</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" s="23" t="n"/>
+      <c r="M33" s="23" t="n"/>
+      <c r="N33" s="23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O33" s="24" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="P33" s="24" t="n">
+        <v>104.97</v>
+      </c>
+      <c r="Q33" s="24" t="n"/>
+      <c r="R33" s="24" t="n"/>
+      <c r="S33" s="23" t="n"/>
+      <c r="T33" s="23" t="n"/>
+      <c r="U33" s="23" t="n"/>
+      <c r="V33" s="23" t="n"/>
+      <c r="W33" s="23" t="n"/>
+      <c r="X33" s="23" t="n"/>
+      <c r="Y33" s="23" t="n"/>
+      <c r="Z33" s="23" t="n"/>
+      <c r="AA33" s="23" t="n"/>
+      <c r="AB33" s="23" t="n"/>
+      <c r="AC33" s="23" t="n"/>
+      <c r="AD33" s="23" t="n"/>
+      <c r="AE33" s="23" t="n"/>
+      <c r="AF33" s="23" t="n"/>
+      <c r="AG33" s="23" t="n"/>
+      <c r="AH33" s="23" t="n"/>
+      <c r="AI33" s="23" t="n"/>
+      <c r="AJ33" s="23" t="n"/>
+      <c r="AK33" s="23" t="n"/>
+    </row>
     <row r="34">
       <c r="A34" s="21" t="n"/>
       <c r="B34" s="21" t="n"/>
       <c r="C34" s="21" t="n"/>
       <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>SYNTHETIC HAIR</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>67041900</t>
+        </is>
+      </c>
       <c r="G34" s="21" t="n"/>
       <c r="H34" s="21" t="n"/>
       <c r="I34" s="21" t="n"/>
       <c r="J34" s="21" t="inlineStr">
         <is>
-          <t>Items on other declaration(s) (2 items)</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="n"/>
+          <t>Faux Locs Crochet Hair Soft Locs 30 inch 6 Packs Long Pre Looped Crochet (1 items)</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="n">
+        <v>2</v>
+      </c>
       <c r="L34" s="21" t="n"/>
       <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
-      <c r="P34" s="22" t="n"/>
-      <c r="Q34" s="21" t="n"/>
-      <c r="R34" s="21" t="n"/>
-      <c r="S34" s="21" t="n"/>
-      <c r="T34" s="21" t="n"/>
-      <c r="U34" s="21" t="n"/>
-      <c r="V34" s="21" t="n"/>
-      <c r="W34" s="21" t="n"/>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O34" s="22" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="P34" s="22" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="Q34" s="22" t="n"/>
+      <c r="R34" s="22" t="n"/>
+      <c r="S34" s="22" t="n"/>
+      <c r="T34" s="22" t="n"/>
+      <c r="U34" s="22" t="n"/>
+      <c r="V34" s="22" t="n"/>
+      <c r="W34" s="22" t="n"/>
       <c r="X34" s="21" t="n"/>
       <c r="Y34" s="21" t="n"/>
       <c r="Z34" s="21" t="n"/>
@@ -2139,179 +2149,151 @@
       <c r="AK34" s="21" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="n"/>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>WIGS</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>67041100</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="21" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>Aauerep Deep Wave Lace Front Wigs Human Hair Wigs for Women (+1 more) (2 items)</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="inlineStr">
+      <c r="A35" s="23" t="n"/>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>AMZ-3</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>Faux Locs Crochet Hair Soft Locs 30 inch 6 Packs Long Pre Looped Crochet</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" s="23" t="n"/>
+      <c r="M35" s="23" t="n"/>
+      <c r="N35" s="23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="O35" s="22" t="n">
-        <v>248.18</v>
-      </c>
-      <c r="P35" s="22" t="n">
-        <v>496.36</v>
-      </c>
-      <c r="Q35" s="22" t="n"/>
-      <c r="R35" s="22" t="n"/>
-      <c r="S35" s="22" t="n"/>
-      <c r="T35" s="22" t="n"/>
-      <c r="U35" s="22" t="n"/>
-      <c r="V35" s="22" t="n"/>
-      <c r="W35" s="22" t="n"/>
-      <c r="X35" s="21" t="n"/>
-      <c r="Y35" s="21" t="n"/>
-      <c r="Z35" s="21" t="n"/>
-      <c r="AA35" s="21" t="n"/>
-      <c r="AB35" s="21" t="n"/>
-      <c r="AC35" s="21" t="n"/>
-      <c r="AD35" s="21" t="n"/>
-      <c r="AE35" s="21" t="n"/>
-      <c r="AF35" s="21" t="n"/>
-      <c r="AG35" s="21" t="n"/>
-      <c r="AH35" s="21" t="n"/>
-      <c r="AI35" s="21" t="n"/>
-      <c r="AJ35" s="21" t="n"/>
-      <c r="AK35" s="21" t="n"/>
+      <c r="O35" s="24" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="P35" s="24" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="Q35" s="24" t="n"/>
+      <c r="R35" s="24" t="n"/>
+      <c r="S35" s="23" t="n"/>
+      <c r="T35" s="23" t="n"/>
+      <c r="U35" s="23" t="n"/>
+      <c r="V35" s="23" t="n"/>
+      <c r="W35" s="23" t="n"/>
+      <c r="X35" s="23" t="n"/>
+      <c r="Y35" s="23" t="n"/>
+      <c r="Z35" s="23" t="n"/>
+      <c r="AA35" s="23" t="n"/>
+      <c r="AB35" s="23" t="n"/>
+      <c r="AC35" s="23" t="n"/>
+      <c r="AD35" s="23" t="n"/>
+      <c r="AE35" s="23" t="n"/>
+      <c r="AF35" s="23" t="n"/>
+      <c r="AG35" s="23" t="n"/>
+      <c r="AH35" s="23" t="n"/>
+      <c r="AI35" s="23" t="n"/>
+      <c r="AJ35" s="23" t="n"/>
+      <c r="AK35" s="23" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="n"/>
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
-      <c r="G36" s="23" t="n"/>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="23" t="inlineStr">
-        <is>
-          <t>AMZ-2</t>
-        </is>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>Aauerep Deep Wave Lace Front Wigs Human Hair Wigs for Women</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" s="23" t="n"/>
-      <c r="M36" s="23" t="n"/>
-      <c r="N36" s="23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O36" s="24" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="P36" s="24" t="n">
-        <v>104.97</v>
-      </c>
-      <c r="Q36" s="24" t="n"/>
-      <c r="R36" s="24" t="n"/>
-      <c r="S36" s="23" t="n"/>
-      <c r="T36" s="23" t="n"/>
-      <c r="U36" s="23" t="n"/>
-      <c r="V36" s="23" t="n"/>
-      <c r="W36" s="23" t="n"/>
-      <c r="X36" s="23" t="n"/>
-      <c r="Y36" s="23" t="n"/>
-      <c r="Z36" s="23" t="n"/>
-      <c r="AA36" s="23" t="n"/>
-      <c r="AB36" s="23" t="n"/>
-      <c r="AC36" s="23" t="n"/>
-      <c r="AD36" s="23" t="n"/>
-      <c r="AE36" s="23" t="n"/>
-      <c r="AF36" s="23" t="n"/>
-      <c r="AG36" s="23" t="n"/>
-      <c r="AH36" s="23" t="n"/>
-      <c r="AI36" s="23" t="n"/>
-      <c r="AJ36" s="23" t="n"/>
-      <c r="AK36" s="23" t="n"/>
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="25" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="25" t="n"/>
+      <c r="F36" s="25" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="25" t="inlineStr">
+        <is>
+          <t>REFERENCE SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="25" t="n"/>
+      <c r="M36" s="25" t="n"/>
+      <c r="N36" s="25" t="n"/>
+      <c r="O36" s="25" t="n"/>
+      <c r="P36" s="26" t="n">
+        <v>123.13</v>
+      </c>
+      <c r="Q36" s="25" t="n"/>
+      <c r="R36" s="25" t="n"/>
+      <c r="S36" s="25" t="n"/>
+      <c r="T36" s="25" t="n"/>
+      <c r="U36" s="25" t="n"/>
+      <c r="V36" s="25" t="n"/>
+      <c r="W36" s="25" t="n"/>
+      <c r="X36" s="25" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="25" t="n"/>
+      <c r="AA36" s="25" t="n"/>
+      <c r="AB36" s="25" t="n"/>
+      <c r="AC36" s="25" t="n"/>
+      <c r="AD36" s="25" t="n"/>
+      <c r="AE36" s="25" t="n"/>
+      <c r="AF36" s="25" t="n"/>
+      <c r="AG36" s="25" t="n"/>
+      <c r="AH36" s="25" t="n"/>
+      <c r="AI36" s="25" t="n"/>
+      <c r="AJ36" s="25" t="n"/>
+      <c r="AK36" s="25" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="23" t="n"/>
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="23" t="n"/>
-      <c r="G37" s="23" t="n"/>
-      <c r="H37" s="23" t="n"/>
-      <c r="I37" s="23" t="inlineStr">
-        <is>
-          <t>AMZ-4</t>
-        </is>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>Queen Story 26 Inch Lace Front Wigs Human Hair 13 x 4 Straight Human</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="23" t="n"/>
-      <c r="M37" s="23" t="n"/>
-      <c r="N37" s="23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O37" s="24" t="n">
-        <v>391.39</v>
-      </c>
-      <c r="P37" s="24" t="n">
-        <v>391.39</v>
-      </c>
-      <c r="Q37" s="24" t="n"/>
-      <c r="R37" s="24" t="n"/>
-      <c r="S37" s="23" t="n"/>
-      <c r="T37" s="23" t="n"/>
-      <c r="U37" s="23" t="n"/>
-      <c r="V37" s="23" t="n"/>
-      <c r="W37" s="23" t="n"/>
-      <c r="X37" s="23" t="n"/>
-      <c r="Y37" s="23" t="n"/>
-      <c r="Z37" s="23" t="n"/>
-      <c r="AA37" s="23" t="n"/>
-      <c r="AB37" s="23" t="n"/>
-      <c r="AC37" s="23" t="n"/>
-      <c r="AD37" s="23" t="n"/>
-      <c r="AE37" s="23" t="n"/>
-      <c r="AF37" s="23" t="n"/>
-      <c r="AG37" s="23" t="n"/>
-      <c r="AH37" s="23" t="n"/>
-      <c r="AI37" s="23" t="n"/>
-      <c r="AJ37" s="23" t="n"/>
-      <c r="AK37" s="23" t="n"/>
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="25" t="n"/>
+      <c r="D37" s="25" t="n"/>
+      <c r="E37" s="25" t="n"/>
+      <c r="F37" s="25" t="n"/>
+      <c r="G37" s="25" t="n"/>
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="25" t="n"/>
+      <c r="J37" s="25" t="inlineStr">
+        <is>
+          <t>REFERENCE FREIGHT</t>
+        </is>
+      </c>
+      <c r="K37" s="25" t="n"/>
+      <c r="L37" s="25" t="n"/>
+      <c r="M37" s="25" t="n"/>
+      <c r="N37" s="25" t="n"/>
+      <c r="O37" s="25" t="n"/>
+      <c r="P37" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q37" s="25" t="n"/>
+      <c r="R37" s="25" t="n"/>
+      <c r="S37" s="25" t="n"/>
+      <c r="T37" s="25" t="n"/>
+      <c r="U37" s="25" t="n"/>
+      <c r="V37" s="25" t="n"/>
+      <c r="W37" s="25" t="n"/>
+      <c r="X37" s="25" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="25" t="n"/>
+      <c r="AA37" s="25" t="n"/>
+      <c r="AB37" s="25" t="n"/>
+      <c r="AC37" s="25" t="n"/>
+      <c r="AD37" s="25" t="n"/>
+      <c r="AE37" s="25" t="n"/>
+      <c r="AF37" s="25" t="n"/>
+      <c r="AG37" s="25" t="n"/>
+      <c r="AH37" s="25" t="n"/>
+      <c r="AI37" s="25" t="n"/>
+      <c r="AJ37" s="25" t="n"/>
+      <c r="AK37" s="25" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="25" t="n"/>
@@ -2325,7 +2307,7 @@
       <c r="I38" s="25" t="n"/>
       <c r="J38" s="25" t="inlineStr">
         <is>
-          <t>REFERENCE SUBTOTAL</t>
+          <t>REFERENCE INSURANCE</t>
         </is>
       </c>
       <c r="K38" s="25" t="n"/>
@@ -2334,7 +2316,7 @@
       <c r="N38" s="25" t="n"/>
       <c r="O38" s="25" t="n"/>
       <c r="P38" s="26" t="n">
-        <v>496.36</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="25" t="n"/>
       <c r="R38" s="25" t="n"/>
@@ -2370,7 +2352,7 @@
       <c r="I39" s="25" t="n"/>
       <c r="J39" s="25" t="inlineStr">
         <is>
-          <t>REFERENCE FREIGHT</t>
+          <t>REFERENCE OTHER COST</t>
         </is>
       </c>
       <c r="K39" s="25" t="n"/>
@@ -2379,7 +2361,7 @@
       <c r="N39" s="25" t="n"/>
       <c r="O39" s="25" t="n"/>
       <c r="P39" s="26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="25" t="n"/>
       <c r="R39" s="25" t="n"/>
@@ -2415,7 +2397,7 @@
       <c r="I40" s="25" t="n"/>
       <c r="J40" s="25" t="inlineStr">
         <is>
-          <t>REFERENCE INSURANCE</t>
+          <t>REFERENCE DEDUCTION</t>
         </is>
       </c>
       <c r="K40" s="25" t="n"/>
@@ -2460,7 +2442,7 @@
       <c r="I41" s="25" t="n"/>
       <c r="J41" s="25" t="inlineStr">
         <is>
-          <t>REFERENCE OTHER COST</t>
+          <t>REFERENCE ADJUSTMENTS</t>
         </is>
       </c>
       <c r="K41" s="25" t="n"/>
@@ -2468,8 +2450,9 @@
       <c r="M41" s="25" t="n"/>
       <c r="N41" s="25" t="n"/>
       <c r="O41" s="25" t="n"/>
-      <c r="P41" s="26" t="n">
-        <v>0</v>
+      <c r="P41" s="26">
+        <f>P37+P38+P39-P40</f>
+        <v/>
       </c>
       <c r="Q41" s="25" t="n"/>
       <c r="R41" s="25" t="n"/>
@@ -2505,7 +2488,7 @@
       <c r="I42" s="25" t="n"/>
       <c r="J42" s="25" t="inlineStr">
         <is>
-          <t>REFERENCE DEDUCTION</t>
+          <t>REFERENCE NET TOTAL</t>
         </is>
       </c>
       <c r="K42" s="25" t="n"/>
@@ -2513,8 +2496,9 @@
       <c r="M42" s="25" t="n"/>
       <c r="N42" s="25" t="n"/>
       <c r="O42" s="25" t="n"/>
-      <c r="P42" s="26" t="n">
-        <v>0</v>
+      <c r="P42" s="26">
+        <f>P36+P41</f>
+        <v/>
       </c>
       <c r="Q42" s="25" t="n"/>
       <c r="R42" s="25" t="n"/>
@@ -2538,52 +2522,6 @@
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="25" t="n"/>
     </row>
-    <row r="43">
-      <c r="A43" s="25" t="n"/>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="25" t="n"/>
-      <c r="D43" s="25" t="n"/>
-      <c r="E43" s="25" t="n"/>
-      <c r="F43" s="25" t="n"/>
-      <c r="G43" s="25" t="n"/>
-      <c r="H43" s="25" t="n"/>
-      <c r="I43" s="25" t="n"/>
-      <c r="J43" s="25" t="inlineStr">
-        <is>
-          <t>REFERENCE ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="K43" s="25" t="n"/>
-      <c r="L43" s="25" t="n"/>
-      <c r="M43" s="25" t="n"/>
-      <c r="N43" s="25" t="n"/>
-      <c r="O43" s="25" t="n"/>
-      <c r="P43" s="26">
-        <f>P39+P40+P41-P42</f>
-        <v/>
-      </c>
-      <c r="Q43" s="25" t="n"/>
-      <c r="R43" s="25" t="n"/>
-      <c r="S43" s="25" t="n"/>
-      <c r="T43" s="25" t="n"/>
-      <c r="U43" s="25" t="n"/>
-      <c r="V43" s="25" t="n"/>
-      <c r="W43" s="25" t="n"/>
-      <c r="X43" s="25" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="25" t="n"/>
-      <c r="AA43" s="25" t="n"/>
-      <c r="AB43" s="25" t="n"/>
-      <c r="AC43" s="25" t="n"/>
-      <c r="AD43" s="25" t="n"/>
-      <c r="AE43" s="25" t="n"/>
-      <c r="AF43" s="25" t="n"/>
-      <c r="AG43" s="25" t="n"/>
-      <c r="AH43" s="25" t="n"/>
-      <c r="AI43" s="25" t="n"/>
-      <c r="AJ43" s="25" t="n"/>
-      <c r="AK43" s="25" t="n"/>
-    </row>
     <row r="44">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="25" t="n"/>
@@ -2596,7 +2534,7 @@
       <c r="I44" s="25" t="n"/>
       <c r="J44" s="25" t="inlineStr">
         <is>
-          <t>REFERENCE NET TOTAL</t>
+          <t>COMBINED ITEMS TOTAL</t>
         </is>
       </c>
       <c r="K44" s="25" t="n"/>
@@ -2605,7 +2543,7 @@
       <c r="N44" s="25" t="n"/>
       <c r="O44" s="25" t="n"/>
       <c r="P44" s="26">
-        <f>P38+P43</f>
+        <f>P5+P36</f>
         <v/>
       </c>
       <c r="Q44" s="25" t="n"/>
@@ -2630,6 +2568,52 @@
       <c r="AJ44" s="25" t="n"/>
       <c r="AK44" s="25" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="25" t="n"/>
+      <c r="B45" s="25" t="n"/>
+      <c r="C45" s="25" t="n"/>
+      <c r="D45" s="25" t="n"/>
+      <c r="E45" s="25" t="n"/>
+      <c r="F45" s="25" t="n"/>
+      <c r="G45" s="25" t="n"/>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
+      <c r="J45" s="25" t="inlineStr">
+        <is>
+          <t>FULL INVOICE FREIGHT</t>
+        </is>
+      </c>
+      <c r="K45" s="25" t="n"/>
+      <c r="L45" s="25" t="n"/>
+      <c r="M45" s="25" t="n"/>
+      <c r="N45" s="25" t="n"/>
+      <c r="O45" s="25" t="n"/>
+      <c r="P45" s="26">
+        <f>P9+P37</f>
+        <v/>
+      </c>
+      <c r="Q45" s="25" t="n"/>
+      <c r="R45" s="25" t="n"/>
+      <c r="S45" s="25" t="n"/>
+      <c r="T45" s="25" t="n"/>
+      <c r="U45" s="25" t="n"/>
+      <c r="V45" s="25" t="n"/>
+      <c r="W45" s="25" t="n"/>
+      <c r="X45" s="25" t="n"/>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="25" t="n"/>
+      <c r="AA45" s="25" t="n"/>
+      <c r="AB45" s="25" t="n"/>
+      <c r="AC45" s="25" t="n"/>
+      <c r="AD45" s="25" t="n"/>
+      <c r="AE45" s="25" t="n"/>
+      <c r="AF45" s="25" t="n"/>
+      <c r="AG45" s="25" t="n"/>
+      <c r="AH45" s="25" t="n"/>
+      <c r="AI45" s="25" t="n"/>
+      <c r="AJ45" s="25" t="n"/>
+      <c r="AK45" s="25" t="n"/>
+    </row>
     <row r="46">
       <c r="A46" s="25" t="n"/>
       <c r="B46" s="25" t="n"/>
@@ -2642,7 +2626,7 @@
       <c r="I46" s="25" t="n"/>
       <c r="J46" s="25" t="inlineStr">
         <is>
-          <t>COMBINED ITEMS TOTAL</t>
+          <t>FULL INVOICE INSURANCE</t>
         </is>
       </c>
       <c r="K46" s="25" t="n"/>
@@ -2651,7 +2635,7 @@
       <c r="N46" s="25" t="n"/>
       <c r="O46" s="25" t="n"/>
       <c r="P46" s="26">
-        <f>P6+P38</f>
+        <f>P10+P38</f>
         <v/>
       </c>
       <c r="Q46" s="25" t="n"/>
@@ -2688,7 +2672,7 @@
       <c r="I47" s="25" t="n"/>
       <c r="J47" s="25" t="inlineStr">
         <is>
-          <t>FULL INVOICE FREIGHT</t>
+          <t>FULL INVOICE OTHER COST</t>
         </is>
       </c>
       <c r="K47" s="25" t="n"/>
@@ -2697,7 +2681,7 @@
       <c r="N47" s="25" t="n"/>
       <c r="O47" s="25" t="n"/>
       <c r="P47" s="26">
-        <f>P10+P39</f>
+        <f>P11+P39</f>
         <v/>
       </c>
       <c r="Q47" s="25" t="n"/>
@@ -2734,7 +2718,7 @@
       <c r="I48" s="25" t="n"/>
       <c r="J48" s="25" t="inlineStr">
         <is>
-          <t>FULL INVOICE INSURANCE</t>
+          <t>FULL INVOICE DEDUCTION</t>
         </is>
       </c>
       <c r="K48" s="25" t="n"/>
@@ -2743,7 +2727,7 @@
       <c r="N48" s="25" t="n"/>
       <c r="O48" s="25" t="n"/>
       <c r="P48" s="26">
-        <f>P11+P40</f>
+        <f>P12+P40</f>
         <v/>
       </c>
       <c r="Q48" s="25" t="n"/>
@@ -2780,7 +2764,7 @@
       <c r="I49" s="25" t="n"/>
       <c r="J49" s="25" t="inlineStr">
         <is>
-          <t>FULL INVOICE OTHER COST</t>
+          <t>FULL ADJUSTMENTS</t>
         </is>
       </c>
       <c r="K49" s="25" t="n"/>
@@ -2789,7 +2773,7 @@
       <c r="N49" s="25" t="n"/>
       <c r="O49" s="25" t="n"/>
       <c r="P49" s="26">
-        <f>P12+P41</f>
+        <f>P45+P46+P47-P48</f>
         <v/>
       </c>
       <c r="Q49" s="25" t="n"/>
@@ -2826,7 +2810,7 @@
       <c r="I50" s="25" t="n"/>
       <c r="J50" s="25" t="inlineStr">
         <is>
-          <t>FULL INVOICE DEDUCTION</t>
+          <t>COMBINED NET TOTAL</t>
         </is>
       </c>
       <c r="K50" s="25" t="n"/>
@@ -2835,7 +2819,7 @@
       <c r="N50" s="25" t="n"/>
       <c r="O50" s="25" t="n"/>
       <c r="P50" s="26">
-        <f>P13+P42</f>
+        <f>P44+P49</f>
         <v/>
       </c>
       <c r="Q50" s="25" t="n"/>
@@ -2872,7 +2856,7 @@
       <c r="I51" s="25" t="n"/>
       <c r="J51" s="25" t="inlineStr">
         <is>
-          <t>FULL ADJUSTMENTS</t>
+          <t>FULL INVOICE TOTAL</t>
         </is>
       </c>
       <c r="K51" s="25" t="n"/>
@@ -2880,9 +2864,8 @@
       <c r="M51" s="25" t="n"/>
       <c r="N51" s="25" t="n"/>
       <c r="O51" s="25" t="n"/>
-      <c r="P51" s="26">
-        <f>P47+P48+P49-P50</f>
-        <v/>
+      <c r="P51" s="26" t="n">
+        <v>613.51</v>
       </c>
       <c r="Q51" s="25" t="n"/>
       <c r="R51" s="25" t="n"/>
@@ -2918,7 +2901,7 @@
       <c r="I52" s="25" t="n"/>
       <c r="J52" s="25" t="inlineStr">
         <is>
-          <t>COMBINED NET TOTAL</t>
+          <t>COMBINED VARIANCE CHECK</t>
         </is>
       </c>
       <c r="K52" s="25" t="n"/>
@@ -2927,7 +2910,7 @@
       <c r="N52" s="25" t="n"/>
       <c r="O52" s="25" t="n"/>
       <c r="P52" s="26">
-        <f>P46+P51</f>
+        <f>P51-P50</f>
         <v/>
       </c>
       <c r="Q52" s="25" t="n"/>
@@ -2952,97 +2935,6 @@
       <c r="AJ52" s="25" t="n"/>
       <c r="AK52" s="25" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="25" t="n"/>
-      <c r="B53" s="25" t="n"/>
-      <c r="C53" s="25" t="n"/>
-      <c r="D53" s="25" t="n"/>
-      <c r="E53" s="25" t="n"/>
-      <c r="F53" s="25" t="n"/>
-      <c r="G53" s="25" t="n"/>
-      <c r="H53" s="25" t="n"/>
-      <c r="I53" s="25" t="n"/>
-      <c r="J53" s="25" t="inlineStr">
-        <is>
-          <t>FULL INVOICE TOTAL</t>
-        </is>
-      </c>
-      <c r="K53" s="25" t="n"/>
-      <c r="L53" s="25" t="n"/>
-      <c r="M53" s="25" t="n"/>
-      <c r="N53" s="25" t="n"/>
-      <c r="O53" s="25" t="n"/>
-      <c r="P53" s="26" t="n">
-        <v>592.51</v>
-      </c>
-      <c r="Q53" s="25" t="n"/>
-      <c r="R53" s="25" t="n"/>
-      <c r="S53" s="25" t="n"/>
-      <c r="T53" s="25" t="n"/>
-      <c r="U53" s="25" t="n"/>
-      <c r="V53" s="25" t="n"/>
-      <c r="W53" s="25" t="n"/>
-      <c r="X53" s="25" t="n"/>
-      <c r="Y53" s="25" t="n"/>
-      <c r="Z53" s="25" t="n"/>
-      <c r="AA53" s="25" t="n"/>
-      <c r="AB53" s="25" t="n"/>
-      <c r="AC53" s="25" t="n"/>
-      <c r="AD53" s="25" t="n"/>
-      <c r="AE53" s="25" t="n"/>
-      <c r="AF53" s="25" t="n"/>
-      <c r="AG53" s="25" t="n"/>
-      <c r="AH53" s="25" t="n"/>
-      <c r="AI53" s="25" t="n"/>
-      <c r="AJ53" s="25" t="n"/>
-      <c r="AK53" s="25" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="25" t="n"/>
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="n"/>
-      <c r="E54" s="25" t="n"/>
-      <c r="F54" s="25" t="n"/>
-      <c r="G54" s="25" t="n"/>
-      <c r="H54" s="25" t="n"/>
-      <c r="I54" s="25" t="n"/>
-      <c r="J54" s="25" t="inlineStr">
-        <is>
-          <t>COMBINED VARIANCE CHECK</t>
-        </is>
-      </c>
-      <c r="K54" s="25" t="n"/>
-      <c r="L54" s="25" t="n"/>
-      <c r="M54" s="25" t="n"/>
-      <c r="N54" s="25" t="n"/>
-      <c r="O54" s="25" t="n"/>
-      <c r="P54" s="26">
-        <f>P53-P52</f>
-        <v/>
-      </c>
-      <c r="Q54" s="25" t="n"/>
-      <c r="R54" s="25" t="n"/>
-      <c r="S54" s="25" t="n"/>
-      <c r="T54" s="25" t="n"/>
-      <c r="U54" s="25" t="n"/>
-      <c r="V54" s="25" t="n"/>
-      <c r="W54" s="25" t="n"/>
-      <c r="X54" s="25" t="n"/>
-      <c r="Y54" s="25" t="n"/>
-      <c r="Z54" s="25" t="n"/>
-      <c r="AA54" s="25" t="n"/>
-      <c r="AB54" s="25" t="n"/>
-      <c r="AC54" s="25" t="n"/>
-      <c r="AD54" s="25" t="n"/>
-      <c r="AE54" s="25" t="n"/>
-      <c r="AF54" s="25" t="n"/>
-      <c r="AG54" s="25" t="n"/>
-      <c r="AH54" s="25" t="n"/>
-      <c r="AI54" s="25" t="n"/>
-      <c r="AJ54" s="25" t="n"/>
-      <c r="AK54" s="25" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
